--- a/data/trans_dic/P19E_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Habitat-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,76; 42,3</t>
+          <t>34,83; 42,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,22; 38,02</t>
+          <t>30,22; 37,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 33,47</t>
+          <t>26,58; 33,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,95</t>
+          <t>17,96; 22,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,39; 36,68</t>
+          <t>31,38; 36,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 28,97</t>
+          <t>24,61; 29,02</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,92; 39,33</t>
+          <t>33,27; 39,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 24,51</t>
+          <t>8,93; 24,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 26,75</t>
+          <t>21,25; 26,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 19,46</t>
+          <t>15,66; 19,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,99; 32,22</t>
+          <t>28,0; 32,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 21,04</t>
+          <t>12,13; 21,17</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,13; 45,09</t>
+          <t>37,68; 45,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,71; 32,16</t>
+          <t>24,45; 32,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,61; 31,24</t>
+          <t>24,66; 31,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 17,41</t>
+          <t>6,74; 17,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,24; 37,04</t>
+          <t>32,08; 37,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 23,27</t>
+          <t>12,36; 23,06</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,65; 28,4</t>
+          <t>22,8; 28,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 24,07</t>
+          <t>18,64; 24,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,44</t>
+          <t>14,6; 19,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,11</t>
+          <t>10,6; 15,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 22,75</t>
+          <t>19,18; 22,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 18,62</t>
+          <t>15,06; 18,82</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,14; 36,55</t>
+          <t>33,11; 36,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 26,57</t>
+          <t>18,67; 26,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,56; 25,24</t>
+          <t>22,52; 25,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,97</t>
+          <t>12,45; 17,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 30,32</t>
+          <t>28,07; 30,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,03; 21,28</t>
+          <t>17,35; 21,29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>227158; 276444</t>
+          <t>227646; 276678</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190115; 239160</t>
+          <t>190087; 237017</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175248; 220879</t>
+          <t>175407; 220537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119802; 153826</t>
+          <t>120386; 150754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>412332; 481729</t>
+          <t>412173; 481727</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>319895; 376426</t>
+          <t>319698; 377118</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>331011; 395451</t>
+          <t>334498; 395917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>121241; 292095</t>
+          <t>106427; 293307</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220908; 275381</t>
+          <t>218804; 276228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147550; 185256</t>
+          <t>149055; 187820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>569614; 655642</t>
+          <t>569920; 653810</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>252188; 451069</t>
+          <t>259986; 453830</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>267915; 325381</t>
+          <t>271936; 326359</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>173920; 226371</t>
+          <t>172068; 225937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184538; 234256</t>
+          <t>184959; 235031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63702; 162103</t>
+          <t>62781; 160729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>474499; 545017</t>
+          <t>472088; 546994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211865; 380445</t>
+          <t>202055; 377047</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>207774; 260527</t>
+          <t>209119; 260399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>172517; 221712</t>
+          <t>171719; 222879</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146669; 197520</t>
+          <t>148383; 201886</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114288; 164279</t>
+          <t>115251; 166886</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>366567; 439868</t>
+          <t>370935; 442559</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>299082; 373904</t>
+          <t>302400; 378026</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1092862; 1205256</t>
+          <t>1091847; 1204950</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>647156; 915610</t>
+          <t>643385; 918610</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>779455; 872098</t>
+          <t>778291; 881775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468059; 617864</t>
+          <t>453223; 618795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1900490; 2047522</t>
+          <t>1895627; 2053835</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1206988; 1507856</t>
+          <t>1229740; 1508502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19E_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,83; 42,34</t>
+          <t>34,21; 42,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,22; 37,68</t>
+          <t>30,07; 37,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,42</t>
+          <t>26,42; 33,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,96; 22,49</t>
+          <t>17,26; 22,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 36,68</t>
+          <t>31,33; 36,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,61; 29,02</t>
+          <t>24,17; 28,56</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,27; 39,37</t>
+          <t>33,06; 39,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 24,62</t>
+          <t>19,72; 25,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 26,83</t>
+          <t>21,61; 26,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 19,73</t>
+          <t>15,4; 19,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 32,13</t>
+          <t>27,83; 32,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,13; 21,17</t>
+          <t>18,47; 21,78</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,68; 45,23</t>
+          <t>37,62; 45,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,45; 32,1</t>
+          <t>24,58; 31,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,66; 31,34</t>
+          <t>24,63; 31,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,26</t>
+          <t>14,75; 19,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,08; 37,17</t>
+          <t>31,89; 36,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 23,06</t>
+          <t>20,41; 24,7</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 28,39</t>
+          <t>22,66; 28,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 24,2</t>
+          <t>17,88; 23,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,87</t>
+          <t>14,6; 19,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,35</t>
+          <t>12,34; 15,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 22,89</t>
+          <t>19,35; 23,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,06; 18,82</t>
+          <t>15,73; 18,83</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,11; 36,54</t>
+          <t>33,07; 36,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,66</t>
+          <t>23,71; 26,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,52</t>
+          <t>22,62; 25,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,0</t>
+          <t>15,74; 17,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,07; 30,41</t>
+          <t>28,13; 30,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,35; 21,29</t>
+          <t>20,02; 21,83</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>212573</t>
+          <t>227820</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135188</t>
+          <t>141949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>347761</t>
+          <t>369769</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>227646; 276678</t>
+          <t>223565; 274670</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190087; 237017</t>
+          <t>205086; 254179</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175407; 220537</t>
+          <t>174362; 221381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120386; 150754</t>
+          <t>125576; 160061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>412173; 481727</t>
+          <t>411439; 483548</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>319698; 377118</t>
+          <t>340663; 402543</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>222677</t>
+          <t>236380</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166593</t>
+          <t>185176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>389270</t>
+          <t>421557</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>334498; 395917</t>
+          <t>332400; 394335</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106427; 293307</t>
+          <t>206620; 265489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218804; 276228</t>
+          <t>222465; 276733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149055; 187820</t>
+          <t>163776; 205730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>569920; 653810</t>
+          <t>566300; 653035</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>259986; 453830</t>
+          <t>389926; 459768</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>199481</t>
+          <t>223721</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119009</t>
+          <t>138218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>318490</t>
+          <t>361939</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>271936; 326359</t>
+          <t>271492; 327603</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172068; 225937</t>
+          <t>196944; 253915</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184959; 235031</t>
+          <t>184687; 234927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62781; 160729</t>
+          <t>119468; 157832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>472088; 546994</t>
+          <t>469216; 543660</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>202055; 377047</t>
+          <t>328843; 397907</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>196628</t>
+          <t>202099</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144525</t>
+          <t>156963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>341153</t>
+          <t>359062</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>209119; 260399</t>
+          <t>207871; 261711</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171719; 222879</t>
+          <t>176034; 227403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148383; 201886</t>
+          <t>148405; 200845</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115251; 166886</t>
+          <t>137187; 174871</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>370935; 442559</t>
+          <t>374053; 446439</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>302400; 378026</t>
+          <t>329788; 394682</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>831359</t>
+          <t>890020</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565315</t>
+          <t>622307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1396675</t>
+          <t>1512326</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1091847; 1204950</t>
+          <t>1090513; 1200348</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>643385; 918610</t>
+          <t>833545; 944961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>778291; 881775</t>
+          <t>781514; 880129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>453223; 618795</t>
+          <t>584212; 663759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1895627; 2053835</t>
+          <t>1899530; 2050258</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1229740; 1508502</t>
+          <t>1447161; 1578159</t>
         </is>
       </c>
     </row>
